--- a/data/kao.xlsx
+++ b/data/kao.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B86D8F4-FEE1-6648-A553-27E5C27944C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AEA8A6-9D2F-7D46-96F7-9E3525026A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="18" r:id="rId1"/>
     <sheet name="Doel" sheetId="6" r:id="rId2"/>
-    <sheet name="Leerplan" sheetId="17" r:id="rId3"/>
-    <sheet name="CombLeerdoelOpleidingsniveau" sheetId="19" r:id="rId4"/>
+    <sheet name="DoelCollectie" sheetId="17" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,14 +30,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="177">
   <si>
     <t>CODE</t>
   </si>
   <si>
-    <t>ingerichtDoor</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -444,9 +440,6 @@
     <t>De leerlingen gebruiken de grootheid vermogen en het Joule-effect om fenomenen in elektrische systemen te verklaren.</t>
   </si>
   <si>
-    <t>leerplan</t>
-  </si>
-  <si>
     <t>II-Nat-d</t>
   </si>
   <si>
@@ -456,30 +449,12 @@
     <t>GO_S-gr2-DoF</t>
   </si>
   <si>
-    <t>versieDatum</t>
-  </si>
-  <si>
-    <t>collectiedoel</t>
-  </si>
-  <si>
-    <t>collectiedoeltype</t>
-  </si>
-  <si>
-    <t>3.0.0</t>
-  </si>
-  <si>
     <t>Studierichting</t>
   </si>
   <si>
-    <t>Natuurwetenschappen</t>
-  </si>
-  <si>
     <t>DT-ET_S-gr2-DoF | DT-CD_S-gr2 | DT-BK_S-gr2</t>
   </si>
   <si>
-    <t>eigenCombinatieLeerdoelOpleidingsniveau</t>
-  </si>
-  <si>
     <t>hetzelfde</t>
   </si>
   <si>
@@ -580,13 +555,19 @@
   </si>
   <si>
     <t>06.49</t>
+  </si>
+  <si>
+    <t>heeftLid</t>
+  </si>
+  <si>
+    <t>Leerplan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,8 +587,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -625,8 +613,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -645,11 +639,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF95B3D7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF95B3D7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -678,6 +683,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1028,15 +1035,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1072,746 +1079,746 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="P1" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -1822,217 +1829,271 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7618F3A8-AF47-B947-A911-1EFF15E07583}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="F3" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="F4" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="F5" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="F6" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="F7" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="F8" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="F9" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="F10" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="F11" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="F12" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14"/>
-      <c r="B14"/>
-      <c r="C14"/>
-      <c r="D14"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
@@ -2047,70 +2108,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB31512-F4D5-024C-AC43-172DAF40B93B}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="8" width="40" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-</worksheet>
 </file>
--- a/data/kao.xlsx
+++ b/data/kao.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AEA8A6-9D2F-7D46-96F7-9E3525026A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98FD3BA-2DAC-0042-82D1-9714D8021D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="18" r:id="rId1"/>
@@ -654,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -683,7 +683,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1222,7 +1221,7 @@
       <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="N7" s="5" t="s">
         <v>147</v>
       </c>
     </row>
@@ -1239,7 +1238,7 @@
       <c r="F8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="N8" s="4" t="s">
         <v>148</v>
       </c>
     </row>
@@ -1256,7 +1255,7 @@
       <c r="F9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="N9" s="5" t="s">
         <v>149</v>
       </c>
     </row>
@@ -1273,7 +1272,7 @@
       <c r="F10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="N10" s="4" t="s">
         <v>150</v>
       </c>
     </row>
@@ -1290,7 +1289,7 @@
       <c r="F11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="N11" s="5" t="s">
         <v>151</v>
       </c>
     </row>
@@ -1307,7 +1306,7 @@
       <c r="F12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="N12" s="4" t="s">
         <v>150</v>
       </c>
     </row>
@@ -1324,7 +1323,7 @@
       <c r="F13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="N13" s="5" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1341,7 +1340,7 @@
       <c r="F14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="N14" s="4" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1443,7 +1442,7 @@
       <c r="F20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="N20" s="4" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1460,7 +1459,7 @@
       <c r="F21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M21" s="5" t="s">
+      <c r="N21" s="5" t="s">
         <v>158</v>
       </c>
     </row>
@@ -1477,7 +1476,7 @@
       <c r="F22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="N22" s="4" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1494,7 +1493,7 @@
       <c r="F23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M23" s="5" t="s">
+      <c r="N23" s="5" t="s">
         <v>159</v>
       </c>
     </row>
@@ -1528,7 +1527,7 @@
       <c r="F25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M25" s="5" t="s">
+      <c r="N25" s="5" t="s">
         <v>161</v>
       </c>
     </row>
@@ -1545,7 +1544,7 @@
       <c r="F26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M26" s="4" t="s">
+      <c r="N26" s="4" t="s">
         <v>161</v>
       </c>
     </row>
@@ -1562,7 +1561,7 @@
       <c r="F27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M27" s="5" t="s">
+      <c r="N27" s="5" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1579,7 +1578,7 @@
       <c r="F28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="N28" s="4" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1596,7 +1595,7 @@
       <c r="F29" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M29" s="5" t="s">
+      <c r="N29" s="5" t="s">
         <v>163</v>
       </c>
     </row>
@@ -1613,7 +1612,7 @@
       <c r="F30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M30" s="4" t="s">
+      <c r="N30" s="4" t="s">
         <v>163</v>
       </c>
     </row>
@@ -1766,7 +1765,7 @@
       <c r="F39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M39" s="5" t="s">
+      <c r="N39" s="5" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1783,7 +1782,7 @@
       <c r="F40" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M40" s="4" t="s">
+      <c r="N40" s="4" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2077,13 +2076,13 @@
       <c r="C14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="8" t="s">
         <v>48</v>
       </c>
       <c r="E14" t="s">
         <v>138</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="12" t="s">
         <v>139</v>
       </c>
     </row>

--- a/data/kao.xlsx
+++ b/data/kao.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98FD3BA-2DAC-0042-82D1-9714D8021D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2A8CCA-11F8-9943-B7BC-CA566BAE4D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -455,9 +455,6 @@
     <t>DT-ET_S-gr2-DoF | DT-CD_S-gr2 | DT-BK_S-gr2</t>
   </si>
   <si>
-    <t>hetzelfde</t>
-  </si>
-  <si>
     <t>06.51</t>
   </si>
   <si>
@@ -561,6 +558,9 @@
   </si>
   <si>
     <t>Leerplan</t>
+  </si>
+  <si>
+    <t>gelijkaardig</t>
   </si>
 </sst>
 </file>
@@ -1071,6 +1071,7 @@
     <col min="13" max="13" width="14.5" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -1120,7 +1121,7 @@
         <v>9</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1137,7 +1138,7 @@
         <v>16</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1154,7 +1155,7 @@
         <v>16</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1171,7 +1172,7 @@
         <v>16</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1188,7 +1189,7 @@
         <v>16</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1205,7 +1206,7 @@
         <v>16</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1222,7 +1223,7 @@
         <v>16</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1239,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1256,7 +1257,7 @@
         <v>16</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1273,7 +1274,7 @@
         <v>16</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1290,7 +1291,7 @@
         <v>16</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1307,7 +1308,7 @@
         <v>16</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1324,7 +1325,7 @@
         <v>16</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1341,7 +1342,7 @@
         <v>16</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1358,7 +1359,7 @@
         <v>16</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1375,7 +1376,7 @@
         <v>16</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1392,7 +1393,7 @@
         <v>16</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1409,7 +1410,7 @@
         <v>16</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1426,7 +1427,7 @@
         <v>16</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1443,7 +1444,7 @@
         <v>16</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1460,7 +1461,7 @@
         <v>16</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1477,7 +1478,7 @@
         <v>16</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1494,7 +1495,7 @@
         <v>16</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1511,7 +1512,7 @@
         <v>16</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1528,7 +1529,7 @@
         <v>16</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1545,7 +1546,7 @@
         <v>16</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1562,7 +1563,7 @@
         <v>16</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1579,7 +1580,7 @@
         <v>16</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1596,7 +1597,7 @@
         <v>16</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1613,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1630,7 +1631,7 @@
         <v>16</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1647,7 +1648,7 @@
         <v>16</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1664,7 +1665,7 @@
         <v>16</v>
       </c>
       <c r="P33" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1681,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1698,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1715,7 +1716,7 @@
         <v>16</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="32" x14ac:dyDescent="0.2">
@@ -1732,7 +1733,7 @@
         <v>16</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1749,7 +1750,7 @@
         <v>16</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1766,7 +1767,7 @@
         <v>16</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1783,7 +1784,7 @@
         <v>16</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1800,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="16" x14ac:dyDescent="0.2">
@@ -1817,7 +1818,7 @@
         <v>16</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -1853,7 +1854,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1</v>
@@ -1876,7 +1877,7 @@
         <v>140</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -1893,7 +1894,7 @@
         <v>43</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -1910,7 +1911,7 @@
         <v>44</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -1927,7 +1928,7 @@
         <v>45</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -1944,7 +1945,7 @@
         <v>46</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -1961,7 +1962,7 @@
         <v>47</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -1978,7 +1979,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -1995,7 +1996,7 @@
         <v>49</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -2012,7 +2013,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -2029,7 +2030,7 @@
         <v>51</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -2046,7 +2047,7 @@
         <v>52</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -2063,7 +2064,7 @@
         <v>53</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">

--- a/data/kao.xlsx
+++ b/data/kao.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2A8CCA-11F8-9943-B7BC-CA566BAE4D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A351EFC-DE98-1946-B36B-E8EBAB6112DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="18" r:id="rId1"/>
     <sheet name="Doel" sheetId="6" r:id="rId2"/>
     <sheet name="DoelCollectie" sheetId="17" r:id="rId3"/>
+    <sheet name="_customVoc" sheetId="19" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="187">
   <si>
     <t>CODE</t>
   </si>
@@ -561,13 +562,43 @@
   </si>
   <si>
     <t>gelijkaardig</t>
+  </si>
+  <si>
+    <t>sheetLabel</t>
+  </si>
+  <si>
+    <t>sheetClass</t>
+  </si>
+  <si>
+    <t>columnLabel</t>
+  </si>
+  <si>
+    <t>columnProperty</t>
+  </si>
+  <si>
+    <t>valueDatatype</t>
+  </si>
+  <si>
+    <t>valueClass</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/2001/XMLSchema#string</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/title</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>http://purl.org/dc/terms/Agent</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -590,6 +621,22 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -651,10 +698,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -684,8 +732,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2108,4 +2159,63 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260A8F22-3C7F-F840-8E37-B5A54CBB3CAA}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{988DFA1F-EC5E-9646-9B4D-FFC40048CC71}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{E35FA191-AFC1-FA4B-BAA7-C7D680E7D05B}"/>
+    <hyperlink ref="E2" r:id="rId3" location="string" xr:uid="{9835B76B-6E96-7847-8104-1C352BE34B11}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/kao.xlsx
+++ b/data/kao.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A351EFC-DE98-1946-B36B-E8EBAB6112DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EED075-0FC9-4247-B799-3596766F9235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="500" windowWidth="37300" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="150" yWindow="150" windowWidth="23010" windowHeight="13650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Agent" sheetId="18" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="179">
   <si>
     <t>CODE</t>
   </si>
@@ -75,9 +75,6 @@
     <t>gerelateerdAan</t>
   </si>
   <si>
-    <t>isSpecialisatieVan</t>
-  </si>
-  <si>
     <t>isBrederDan</t>
   </si>
   <si>
@@ -87,12 +84,6 @@
     <t>Katholiek Onderwijs Vlaanderen</t>
   </si>
   <si>
-    <t>Leerplannen van het secundair volwassenenonderwijs</t>
-  </si>
-  <si>
-    <t>Leerplannen van de basiseducatie</t>
-  </si>
-  <si>
     <t>Leerplan van het basisonderwijs</t>
   </si>
   <si>
@@ -123,12 +114,6 @@
     <t>Leerplannen van het 7de leerjaar secundair onderwijs</t>
   </si>
   <si>
-    <t>VOV_SV</t>
-  </si>
-  <si>
-    <t>VOV_V-B</t>
-  </si>
-  <si>
     <t>KaO_K&amp;L</t>
   </si>
   <si>
@@ -159,12 +144,6 @@
     <t>KaO_S-lj7</t>
   </si>
   <si>
-    <t>SV</t>
-  </si>
-  <si>
-    <t>V-B</t>
-  </si>
-  <si>
     <t>K | L</t>
   </si>
   <si>
@@ -447,15 +426,9 @@
     <t>SR-Nat_S-gr2-DoF</t>
   </si>
   <si>
-    <t>GO_S-gr2-DoF</t>
-  </si>
-  <si>
     <t>Studierichting</t>
   </si>
   <si>
-    <t>DT-ET_S-gr2-DoF | DT-CD_S-gr2 | DT-BK_S-gr2</t>
-  </si>
-  <si>
     <t>06.51</t>
   </si>
   <si>
@@ -592,13 +565,16 @@
   </si>
   <si>
     <t>http://purl.org/dc/terms/Agent</t>
+  </si>
+  <si>
+    <t>heeftSpecialisatie</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,6 +613,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -702,16 +684,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -722,24 +698,236 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="25">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -750,6 +938,57 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F47F6B35-AD23-4BFC-A55D-31B50091883E}" name="Table1" displayName="Table1" ref="A1:B2" totalsRowShown="0" headerRowDxfId="21" dataDxfId="22">
+  <autoFilter ref="A1:B2" xr:uid="{F47F6B35-AD23-4BFC-A55D-31B50091883E}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{A284B441-C82E-4AFE-A846-8A5A44C7A09B}" name="CODE" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{40B2BE62-89EC-4662-B787-847975BBF79B}" name="naam" dataDxfId="23"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8341B52E-832B-495B-9A05-34E5057556C8}" name="Table2" displayName="Table2" ref="A1:P42" totalsRowShown="0" headerRowDxfId="8" dataDxfId="9">
+  <autoFilter ref="A1:P42" xr:uid="{8341B52E-832B-495B-9A05-34E5057556C8}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{61AECCC0-C1B3-4EAC-83FB-42641F37BF72}" name="CODE" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{BC4D7687-E133-4285-81FE-60AB0FB15D40}" name="beschrijving" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{0F9367F6-5D72-4DA2-9759-7F77B0485E84}" name="geldigheid" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{D14167CD-0A38-48B1-9E7C-45FB185AD8A2}" name="identificator" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{F68C6B5A-26E0-4B50-BC39-F74A5028C3EB}" name="niveau" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{30F09F61-5288-4457-A4EE-A94CB3A32A8B}" name="gedefinieerdDoor" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{6CF1F655-00EA-4DD5-AFBD-8E69B6B88D61}" name="onderwerp" dataDxfId="17"/>
+    <tableColumn id="8" xr3:uid="{A362D5E7-68EC-4588-8AB3-F7A40542B441}" name="type" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{D837FFA8-F5A0-40A1-8E47-1DE65BE4E956}" name="bron" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{BF9E0441-4EC4-4338-89CD-13D9EF24B79E}" name="doelgroep" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{52D9B432-C1BA-4B73-AEDD-6E558568618B}" name="competentie" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{5A3562EC-D0EA-4689-A207-0F3714255E50}" name="gerelateerdAan" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{967B2F07-1531-4DEF-AE84-FD9C982C5B49}" name="heeftSpecialisatie" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{6F18B6FB-016B-4F60-9ECC-DEF1F9DE2E52}" name="isBrederDan" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{83D9DF61-79AC-4BE7-8675-37B21990A207}" name="bestaatUit" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{EE2BE5F5-A665-45B3-B216-C794FB05D638}" name="gelijkaardig"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4A34FA34-CE4C-4840-9040-460B5225DFF0}" name="Table3" displayName="Table3" ref="A1:F12" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:F12" xr:uid="{4A34FA34-CE4C-4840-9040-460B5225DFF0}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{B2A14018-0CB9-4755-B5E6-1D2F6B32A3D8}" name="CODE" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{76CB90B7-93B0-46E0-8DBA-EE8DB2E781DC}" name="naam"/>
+    <tableColumn id="3" xr3:uid="{2E88711B-F425-43FC-8A3C-3BED76EEDE9F}" name="gedefinieerdDoor" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{D9D764B1-9D20-4068-ADBB-E064636F10C2}" name="niveau"/>
+    <tableColumn id="5" xr3:uid="{AC0C51DD-0AD8-4140-89B7-B41A00A837B0}" name="heeftLid"/>
+    <tableColumn id="6" xr3:uid="{93310496-7E9D-4CC8-8A93-064B48DE6BF1}" name="type" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1075,1139 +1314,1139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E48475DD-7AAE-7649-996C-7728C46BB2FB}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="40" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="98.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.42578125" style="16" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="N1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="P1" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B9" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="4" t="s">
+      <c r="F9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P3" s="5" t="s">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" s="4" t="s">
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P5" s="5" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P16" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P6" s="4" t="s">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P17" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="5" t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P18" s="2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N8" s="4" t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P19" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N9" s="5" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N10" s="4" t="s">
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M22" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N11" s="5" t="s">
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P24" s="2" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N13" s="5" t="s">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N14" s="4" t="s">
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M26" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P15" s="5" t="s">
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M27" s="3" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P16" s="4" t="s">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="N28" s="2"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P17" s="5" t="s">
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P31" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P18" s="4" t="s">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P32" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P19" s="5" t="s">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P33" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N20" s="4" t="s">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P34" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N21" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N22" s="4" t="s">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P35" s="3" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P24" s="4" t="s">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P36" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N25" s="5" t="s">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P37" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N27" s="5" t="s">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P38" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N29" s="5" t="s">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N30" s="4" t="s">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P31" s="5" t="s">
+      <c r="N40" s="2"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P41" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P32" s="4" t="s">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P42" s="2" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P33" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P34" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A35" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P35" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P36" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="A37" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P37" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N39" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N40" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P41" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7618F3A8-AF47-B947-A911-1EFF15E07583}">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="60" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="F7" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="F8" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="F9" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="F10" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>28</v>
+      <c r="F11" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
     </row>
-    <row r="17" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="18" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="19" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="20" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="21" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="17" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260A8F22-3C7F-F840-8E37-B5A54CBB3CAA}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>186</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>183</v>
+      <c r="D2" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
